--- a/artfynd/A 50170-2025 artfynd.xlsx
+++ b/artfynd/A 50170-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55265920</v>
+        <v>58818084</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>356</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Labyrintlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Claurouxia chalybeioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullsågen, Dlr</t>
+          <t>Håjensån, Kullsågen, vid mynningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491488.2077183144</v>
+        <v>491598</v>
       </c>
       <c r="R2" t="n">
-        <v>6690206.773391959</v>
+        <v>6690355</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,37 +769,22 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Triviallövskog</t>
+          <t>Blockstrand vid sötvatten</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>igenväxt gammal brukad mark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>60 cm grovt träd</t>
+          <t>rensad å med stora block och hällar</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Sur bergart</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # gammalt bävergnag på levande träd # Populus tremula # 60 cm grovt träd</t>
+          <t>Acidic rock # häll som tidvis översvämmas i strömmande vattendrag</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -829,6 +799,148 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>55265920</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kullsågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>491488</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6690207</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-09-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Triviallövskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>igenväxt gammal brukad mark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>60 cm grovt träd</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # gammalt bävergnag på levande träd # Populus tremula # 60 cm grovt träd</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
